--- a/05_Figures/F06_prediction/proteins/training/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,24 +131,27 @@
     <t xml:space="preserve">DCTN1</t>
   </si>
   <si>
+    <t xml:space="preserve">SERBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETF1</t>
+  </si>
+  <si>
     <t xml:space="preserve">PKLR</t>
   </si>
   <si>
-    <t xml:space="preserve">SERBP1</t>
+    <t xml:space="preserve">SMTNL1</t>
   </si>
   <si>
     <t xml:space="preserve">ACADM</t>
   </si>
   <si>
-    <t xml:space="preserve">AHCYL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF1</t>
-  </si>
-  <si>
     <t xml:space="preserve">HSP90B1</t>
   </si>
   <si>
@@ -161,12 +164,12 @@
     <t xml:space="preserve">PGM5</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL6</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS17</t>
   </si>
   <si>
-    <t xml:space="preserve">SMTNL1</t>
-  </si>
-  <si>
     <t xml:space="preserve">TIMM44</t>
   </si>
   <si>
@@ -185,370 +188,343 @@
     <t xml:space="preserve">NDUFAB1</t>
   </si>
   <si>
+    <t xml:space="preserve">SLK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YWHAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NXN</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMA5</t>
   </si>
   <si>
-    <t xml:space="preserve">SLK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEMO1</t>
+    <t xml:space="preserve">SOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAB39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL1</t>
   </si>
   <si>
     <t xml:space="preserve">MYH14</t>
   </si>
   <si>
-    <t xml:space="preserve">NXN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YWHAH</t>
+    <t xml:space="preserve">PDIA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLASP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD1L</t>
   </si>
   <si>
     <t xml:space="preserve">AARSD1</t>
   </si>
   <si>
-    <t xml:space="preserve">CAB39</t>
-  </si>
-  <si>
     <t xml:space="preserve">COPS2</t>
   </si>
   <si>
-    <t xml:space="preserve">PDIA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASP2</t>
-  </si>
-  <si>
     <t xml:space="preserve">GLO1</t>
   </si>
   <si>
-    <t xml:space="preserve">GPD1L</t>
+    <t xml:space="preserve">INPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STXBP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCN</t>
   </si>
   <si>
     <t xml:space="preserve">DHRS4</t>
   </si>
   <si>
-    <t xml:space="preserve">INPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCN</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSMD2</t>
   </si>
   <si>
+    <t xml:space="preserve">AHSA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPDR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACOT9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH9A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAND2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX39B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNPEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4EBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXYD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNPDA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSDL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAT2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCCC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTRES1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCIAD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBXIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIP4K2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRXL2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNF123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCRN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTAN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMED2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM126A</t>
+  </si>
+  <si>
     <t xml:space="preserve">TMX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHSA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPDR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRXL2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STXBP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH9A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAND2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX39B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHODH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FXYD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GHITM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNPDA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPHN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSDL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILF3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAT2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCCC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTRES1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCIAD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBXIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP4K2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNF123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWDD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCRN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTAN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMED2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM126A</t>
   </si>
   <si>
     <t xml:space="preserve">TSN</t>
@@ -950,16 +926,16 @@
         <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.463929410300316</v>
+        <v>-0.665665988640693</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.104683592816943</v>
+        <v>-0.0468321336286322</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -983,29 +959,21 @@
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.463929410300316</v>
+        <v>-0.665665988640693</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.104683592816943</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.462686567164179</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.472636815920398</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.670880984376335</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.756538096386816</v>
-      </c>
+        <v>-0.0468321336286322</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1029,2206 +997,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.92258168697856</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.04827552959427</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.460478711210967</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.590501515576271</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.32243622903252</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.0766050936903175</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.141187250729571</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.524811076807682</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.330975671851702</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.52530200625465</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.7499368002396</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-2.23549971932769</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.341477059548148</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.189230050836791</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.587858699152537</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.371387736697764</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.376694994377133</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.464132004871335</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.976130098666001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.69154024467225</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.164607585583349</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.236069907506127</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.160157927399748</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.909575122132716</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.448201924386208</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-2.45924937529229</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.32116008448145</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.496910054476145</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-4.21188096596125</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.291279153375934</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.607712345130086</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.05501937373061</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.530930462950511</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.54210650656322</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.995863684529986</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.576727544591828</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.151360064504611</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.302981431402389</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.15730725878642</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-2.62044536737119</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.399535917773133</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.59030051181076</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.0457433081943741</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.15333059031585</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.465035519844508</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.0460344905728389</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-1.41402490550491</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.723542022437506</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.910580715618526</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.588733277639326</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.676895197903977</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.36993189201936</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.295395526229665</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.140921339583717</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.197081184696766</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.170743173522752</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.02809725923549</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.144960575138884</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.26891397882655</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.269634831539051</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.0166395840580928</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.64852279634845</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.626897596014567</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.943590258781305</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.441543160226346</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.523218041576577</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.650033482305634</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.43219351073029</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.9496472473787</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.0630856500956809</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.2375800639644</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.287292647212452</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.0381362705957</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.0683698718565937</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.45047922619242</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.692136332584824</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.0102684751255463</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.982016371563167</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.379233718434463</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.743484961306699</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.609466469085079</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.248098954025689</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.22150864193895</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.26950555516537</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.942601106283658</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.654684952468004</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.44002633587086</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.603361117264281</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.230118765871165</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.82902357841809</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.48693920250532</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.279057258884582</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.54422437906268</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.41008513793294</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.46794000033076</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.403074798410517</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-1.27692336744394</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-2.93916990350014</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.391813706483779</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.47520952833076</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-2.45416576691431</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.678008382417103</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.22857998685763</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.354227627303935</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.734722809553982</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.38728473567034</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.197196429203521</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-1.27240730630727</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.144551789687861</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.976883960356072</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.648708415406388</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.68020871830673</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.540748175490806</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.326054104028376</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.1818063000009</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.294980010047159</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.1809327439118</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.422401202844539</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.925068406328692</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.847318748670248</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.471427796612059</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.19709429292955</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.273921570008438</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.0243043260199551</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.945190400141581</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0.635656475638879</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0.129859776872343</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.720487748572914</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.082914901046331</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0.116628484359612</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.279471560052813</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.537581995827073</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.397065635356342</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.382130391663349</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.103997456880697</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.428809258507672</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.30814610625554</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.03172237014343</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.814710480206417</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0.0649253330927014</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0.238427250170469</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-2.10648265510372</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.47890733224566</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.237459761751634</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.913372949499472</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.0755736347353078</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.02066368660978</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.69543267328017</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.97940967676026</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.199617353013325</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0.55412279587828</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0.262666128738452</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.4115345273491</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.302023725930606</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.12972759816625</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.77460579110846</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.14324974701119</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.84329223769645</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.56820215143039</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.268117094175772</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.879866353114983</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.0977136502091773</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.471345936753191</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0.215190638866203</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.0667183790494752</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.615755406037112</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.201964974753779</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.29660990714007</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.431872910692798</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.2351149165887</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.0331125147053419</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.01147570739175</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.0265017549641741</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.571866612242174</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.806875634843622</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.45918016640028</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.789910823747589</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.05167623990616</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-2.15908971099064</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.35770007761422</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-1.2076494222371</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.376121844352431</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.308177091284962</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.308258997936953</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.446898563985698</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.198596010868292</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.106221310645753</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.947992329204169</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.23148627930535</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.196647734429786</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>0.10900676879035</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.25637414280189</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.46091380789814</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.518485741194127</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.0382138291023593</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.16105968320093</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-1.99211569741732</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0.000933020959894337</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.5941460125232</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-2.75941920989821</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3271,7 +1039,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.70533606381504</v>
+        <v>2.91290210073778</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +1056,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9980543176692</v>
+        <v>12.2660039914314</v>
       </c>
     </row>
     <row r="4">
@@ -3305,7 +1073,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>12.709159196665</v>
+        <v>12.2165463840293</v>
       </c>
     </row>
     <row r="5">
@@ -3322,7 +1090,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>11.4167483573276</v>
+        <v>12.1288058539271</v>
       </c>
     </row>
     <row r="6">
@@ -3339,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>4.54023705774726</v>
+        <v>4.93948714656527</v>
       </c>
     </row>
     <row r="7">
@@ -3356,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>11.940472205839</v>
+        <v>17.8383931644117</v>
       </c>
     </row>
     <row r="8">
@@ -3373,7 +1141,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>8.75099025197988</v>
+        <v>8.79441842455479</v>
       </c>
     </row>
     <row r="9">
@@ -3390,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>11.4384018214552</v>
+        <v>11.4631763140815</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1038018843649</v>
+        <v>10.0662426182215</v>
       </c>
     </row>
     <row r="11">
@@ -3424,7 +1192,7 @@
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>9.21938600716511</v>
+        <v>9.65474109200348</v>
       </c>
     </row>
     <row r="12">
@@ -3441,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>6.91845626872274</v>
+        <v>6.69808267607916</v>
       </c>
     </row>
     <row r="13">
@@ -3458,7 +1226,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>2.38698374218636</v>
+        <v>2.33955393549476</v>
       </c>
     </row>
     <row r="14">
@@ -3475,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>9.62674128525642</v>
+        <v>9.61218133669221</v>
       </c>
     </row>
   </sheetData>
@@ -3568,10 +1336,10 @@
         <v>39</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.846153846153846</v>
+        <v>0.769230769230769</v>
       </c>
     </row>
     <row r="6">
@@ -3653,10 +1421,10 @@
         <v>44</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="11">
@@ -3670,10 +1438,10 @@
         <v>45</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="12">
@@ -3687,10 +1455,10 @@
         <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="13">
@@ -3704,10 +1472,10 @@
         <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="14">
@@ -3721,10 +1489,10 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="15">
@@ -3738,10 +1506,10 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="16">
@@ -3755,10 +1523,10 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="17">
@@ -3772,10 +1540,10 @@
         <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.769230769230769</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="18">
@@ -3806,10 +1574,10 @@
         <v>53</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.692307692307692</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="20">
@@ -3823,10 +1591,10 @@
         <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.692307692307692</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="21">
@@ -3840,10 +1608,10 @@
         <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.692307692307692</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="22">
@@ -3857,10 +1625,10 @@
         <v>56</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0.692307692307692</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="23">
@@ -3874,10 +1642,10 @@
         <v>57</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0.692307692307692</v>
+        <v>0.615384615384615</v>
       </c>
     </row>
     <row r="24">
@@ -3942,10 +1710,10 @@
         <v>61</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.615384615384615</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="28">
@@ -3959,10 +1727,10 @@
         <v>62</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>0.615384615384615</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="29">
@@ -3976,10 +1744,10 @@
         <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>0.615384615384615</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="30">
@@ -3993,10 +1761,10 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.615384615384615</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="31">
@@ -4010,10 +1778,10 @@
         <v>65</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>0.615384615384615</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="32">
@@ -4044,10 +1812,10 @@
         <v>67</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.538461538461538</v>
+        <v>0.461538461538462</v>
       </c>
     </row>
     <row r="34">
@@ -4061,10 +1829,10 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.538461538461538</v>
+        <v>0.461538461538462</v>
       </c>
     </row>
     <row r="35">
@@ -4129,10 +1897,10 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.461538461538462</v>
+        <v>0.384615384615385</v>
       </c>
     </row>
     <row r="39">
@@ -4163,10 +1931,10 @@
         <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.384615384615385</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="41">
@@ -4180,10 +1948,10 @@
         <v>75</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.384615384615385</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="42">
@@ -4197,10 +1965,10 @@
         <v>76</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.384615384615385</v>
+        <v>0.307692307692308</v>
       </c>
     </row>
     <row r="43">
@@ -4350,10 +2118,10 @@
         <v>85</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0.230769230769231</v>
+        <v>0.153846153846154</v>
       </c>
     </row>
     <row r="52">
@@ -4554,10 +2322,10 @@
         <v>97</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="64">
@@ -4571,10 +2339,10 @@
         <v>98</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="65">
@@ -4588,10 +2356,10 @@
         <v>99</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="66">
@@ -4605,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="67">
@@ -4622,10 +2390,10 @@
         <v>101</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="68">
@@ -4639,10 +2407,10 @@
         <v>102</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
     </row>
     <row r="69">
@@ -5866,142 +3634,6 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="s">
-        <v>175</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="s">
-        <v>176</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="s">
-        <v>177</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>178</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="s">
-        <v>179</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="s">
-        <v>180</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="s">
-        <v>181</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="s">
-        <v>182</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
         <v>0.0769230769230769</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/training/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_1rm_ext/spls/c_data/results.xlsx
@@ -962,7 +962,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.665665988640693</v>
@@ -970,10 +970,18 @@
       <c r="I3" t="n">
         <v>-0.0468321336286322</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.557213930348259</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.427860696517413</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.663287847784656</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.744394154810536</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -997,6 +1005,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.789148320842511</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.26608639709543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.58681791588025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.694785639322231</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.03591689212327</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.153291699543151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.382495192560736</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.90455126859329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.0420556079569181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.689233290830522</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.53802800017259</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-2.15984391998739</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.28548690346306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.203231604247696</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.614187419736324</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.384297769147486</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.395010823908777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.312862572608336</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.04629430870951</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.23791974173585</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.183803804182882</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.165675198346477</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.201948773568114</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.37999661307148</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.461661453032122</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-2.52682586904441</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.48415274707879</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.497506297102512</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-3.75753086817944</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.240166602588027</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.861818648823667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.19124197604621</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.436039341131868</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.33831663010365</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.942444964711894</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.572052954174179</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.0829490335999503</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.394809366169613</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.88524029265211</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.5961556295826</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.381003328382685</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.60128660335401</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.0301227744750874</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.05862680338697</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.147067109403058</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.646404214899331</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-3.20355871496337</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.09908611477088</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.780696462708256</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.906274545816991</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.693864403823597</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-2.34732883600443</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.822185847049246</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.159537034280261</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.122856501872867</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.330729872267681</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.793568190423417</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.28152935801665</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.32366270925462</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.375287950323975</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.0581436634035447</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.308196883378844</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.572264204506436</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.869301556299829</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.519493762393148</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.573023339112403</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.573901589026761</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.09292132220322</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.824807539853412</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.184053672610256</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.03790370001614</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.264659751280253</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-2.27385420525452</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.567191701464959</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.07551254662407</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.604393017922657</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.0109093624422285</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.947580912871394</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.188183350677273</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.956627342188259</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.493136959565814</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.295192033163967</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.945312688061142</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.29577764936331</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.607414047479038</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.663712760676392</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.58520841971093</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.20104069754367</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.311058500945479</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.84043370610527</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.442850918981091</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.298593015354568</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.56119753436516</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.58152067987046</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.91531231231673</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.407073430647092</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.18400019346305</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-2.34301566093751</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.314242777582095</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.38276238785984</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-2.20351136830982</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.816046760959482</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.140767096211735</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.242551875311769</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.122977097957464</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.65376307522759</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.15781501234</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.2089727473655</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.128032000158197</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.29800225518187</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.734568130953791</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.70938627902813</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.310562631392568</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.40086622385192</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.223686995469682</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.375479330529614</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.40022063815424</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.380353909479276</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.995568256509993</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.968292805037186</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.553198186036595</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.754313528477508</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.319360496086517</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.153541865075489</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.945745304168522</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.620524204999229</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.10860119962587</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.750561501400996</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.085717010045874</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.248228694136392</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.0449726921915286</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.696057335080966</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.32809047303932</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.442502715266092</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.0148217028969084</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.157724107749681</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.26703847150084</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.750629903291644</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.787538998030475</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.0129042199794045</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.385284701479355</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1.77630751331347</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.49328933495109</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.666148347597778</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.893800888164667</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.257334754377199</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.02356774106821</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-1.18214218486885</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.607567514951032</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.362633077730507</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.527215821554691</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.387644724012951</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.26251783209552</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.371731505138776</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.02847628365665</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.75616501052139</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.996836576557703</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.86971205506923</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.27858715826031</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.106637730038588</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.707826034970399</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.393176737976392</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.503655167752822</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.0852991964929003</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.181839657947099</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.983893851990944</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.214689698154476</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.25392417529138</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.421164577076428</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.58611222304621</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.301707881246371</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.638205993666639</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.122182099009637</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.671524412852267</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.723267847327885</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.487761403749333</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.754028378333444</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.977050530663541</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-2.2362339130823</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.394858499547691</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.19684993285632</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.467499596297263</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.243114609792516</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.210291044939549</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.45801646423917</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.209788041374256</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.284325471551501</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1.23942130526113</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.313254876934951</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.16135454597425</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.119579916410763</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.38097223756872</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.48847431042636</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.516693180476396</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.0185538769575853</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.0682198126691</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-2.21000219297474</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.358521608977747</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.33336385315069</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-2.46101387189575</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
